--- a/JsonConverter/ExcelFiles/EnemySkill.xlsx
+++ b/JsonConverter/ExcelFiles/EnemySkill.xlsx
@@ -5,7 +5,7 @@
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\goo30\OneDrive\바탕 화면\게임 공부\1차 팀프로젝트\엑셀파일\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\NRUnityProjects\ACE\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
@@ -21,7 +21,76 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="73">
   <x:si>
+    <x:t>텍스처가 덜 입혀진 몸으로 그냥 부딪힘</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대충 만든 슬라임이라 펀치도 흐물흐물함</x:t>
+  </x:si>
+  <x:si>
+    <x:t>눈에서 나가는 레이저인데 딱 봐도 이펙트가 싸구려임</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Untextured Slam</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>위력</x:t>
+  </x:si>
+  <x:si>
+    <x:t>설명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>적ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillDescription</x:t>
+  </x:si>
+  <x:si>
+    <x:t>enemySkill_07_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>enemySkill_03_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>enemySkill_02_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>enemySkill_04_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>enemySkill_01_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>저예산 좀비라 이빨 모델링이 대충임</x:t>
+  </x:si>
+  <x:si>
+    <x:t>enemySkill_06_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>enemySkill_05_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TargetSelectType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Recycled Screech</x:t>
+  </x:si>
+  <x:si>
     <x:t>SkillType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Fake Laser</x:t>
+  </x:si>
+  <x:si>
+    <x:t>타겟 선택 방식</x:t>
+  </x:si>
+  <x:si>
+    <x:t>enemy_03</x:t>
   </x:si>
   <x:si>
     <x:t>TargetType</x:t>
@@ -30,34 +99,16 @@
     <x:t>TargetCount</x:t>
   </x:si>
   <x:si>
-    <x:t>SkillDescription</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Power</x:t>
-  </x:si>
-  <x:si>
-    <x:t>타겟 선택 방식</x:t>
+    <x:t>재사용 대기시간</x:t>
   </x:si>
   <x:si>
     <x:t>enemy_07</x:t>
   </x:si>
   <x:si>
-    <x:t>재사용 대기시간</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Fake Laser</x:t>
-  </x:si>
-  <x:si>
-    <x:t>enemy_03</x:t>
-  </x:si>
-  <x:si>
     <x:t>enemy_01</x:t>
   </x:si>
   <x:si>
-    <x:t>enemy_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>enemy_04</x:t>
+    <x:t>enemy_02</x:t>
   </x:si>
   <x:si>
     <x:t>enemy_06</x:t>
@@ -69,40 +120,106 @@
     <x:t>Maybe Punch</x:t>
   </x:si>
   <x:si>
+    <x:t>enemy_05</x:t>
+  </x:si>
+  <x:si>
     <x:t>Cheap Bite</x:t>
   </x:si>
   <x:si>
     <x:t>Wobbly Whip</x:t>
   </x:si>
   <x:si>
-    <x:t>enemy_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>설명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>위력</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>적ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>눈에서 나가는 레이저인데 딱 봐도 이펙트가 싸구려임</x:t>
+    <x:t>enemy_04</x:t>
   </x:si>
   <x:si>
     <x:t>ActionType</x:t>
   </x:si>
   <x:si>
-    <x:t>TargetSelectType</x:t>
+    <x:t>CoolTime</x:t>
   </x:si>
   <x:si>
-    <x:t>임시적02</x:t>
+    <x:t>SkillNameEn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillName</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EnemyName</x:t>
+  </x:si>
+  <x:si>
+    <x:t>다른 게임에서 가져온 듯한 효과음으로 괴성을 지름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>관절 렌더링이 덜 돼서 삐걱거리며 팔을 휘두름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>물리 연산이 이상해서 촉수가 제멋대로 흐느적거림</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스킬ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>레이저쏘기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>임시적04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>타겟 범위</x:t>
+  </x:si>
+  <x:si>
+    <x:t>행동타입</x:t>
+  </x:si>
+  <x:si>
+    <x:t>물어뜯기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Single</x:t>
+  </x:si>
+  <x:si>
+    <x:t>몸통박치기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Attack</x:t>
+  </x:si>
+  <x:si>
+    <x:t>타겟 수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>임시적07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>휘두르기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>삐걱펀치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스킬이름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>임시적05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EnemyId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>임시적03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스킬이름영문</x:t>
+  </x:si>
+  <x:si>
+    <x:t>적 이름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>임시적01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대충펀치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>임시적06</x:t>
   </x:si>
   <x:si>
     <x:t>string</x:t>
@@ -114,130 +231,13 @@
     <x:t>괴성지르기</x:t>
   </x:si>
   <x:si>
-    <x:t>임시적06</x:t>
+    <x:t>임시적02</x:t>
   </x:si>
   <x:si>
-    <x:t>대충펀치</x:t>
+    <x:t>Power</x:t>
   </x:si>
   <x:si>
-    <x:t>레이저쏘기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Single</x:t>
-  </x:si>
-  <x:si>
-    <x:t>휘두르기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>몸통박치기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>임시적07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Attack</x:t>
-  </x:si>
-  <x:si>
-    <x:t>삐걱펀치</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스킬ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>임시적04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>타겟 수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스킬이름영문</x:t>
-  </x:si>
-  <x:si>
-    <x:t>행동타입</x:t>
-  </x:si>
-  <x:si>
-    <x:t>임시적01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스킬이름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>적 이름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>임시적03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>물어뜯기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>임시적05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>타겟 범위</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkillNameEn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>enemySkill_02_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>enemySkill_05_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>enemySkill_03_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>저예산 좀비라 이빨 모델링이 대충임</x:t>
-  </x:si>
-  <x:si>
-    <x:t>enemySkill_07_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>enemySkill_04_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>enemySkill_01_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Recycled Screech</x:t>
-  </x:si>
-  <x:si>
-    <x:t>enemySkill_06_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>물리 연산이 이상해서 촉수가 제멋대로 흐느적거림</x:t>
-  </x:si>
-  <x:si>
-    <x:t>다른 게임에서 가져온 듯한 효과음으로 괴성을 지름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>관절 렌더링이 덜 돼서 삐걱거리며 팔을 휘두름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RandomFriendly</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Untextured Slam</x:t>
-  </x:si>
-  <x:si>
-    <x:t>텍스처가 덜 입혀진 몸으로 그냥 부딪힘</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대충 만든 슬라임이라 펀치도 흐물흐물함</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EnemyName</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CoolTime</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkillName</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EnemyId</x:t>
+    <x:t>RandomEnemy</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1368,156 +1368,156 @@
   <x:sheetData>
     <x:row r="1" spans="1:13" s="7" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A1" s="6" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B1" s="6" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C1" s="6" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="D1" s="6" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="E1" s="6" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="F1" s="6" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="G1" s="6" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="H1" s="6" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="I1" s="6" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="J1" s="6" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="K1" s="6" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="L1" s="21" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="M1" s="21" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:14" s="7" customFormat="1" ht="13.199999999999999">
+      <x:c r="A2" s="6" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="B2" s="6" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="C2" s="6" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="D2" s="6" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="E2" s="6" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="F2" s="6" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="G2" s="6" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="H2" s="6" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="I2" s="6" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="J2" s="6" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K2" s="6" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="L2" s="21" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="M2" s="21" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="N2" s="6"/>
+    </x:row>
+    <x:row r="3" spans="1:14" s="10" customFormat="1" ht="15.75" customHeight="1">
+      <x:c r="A3" s="8" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B3" s="8" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="C3" s="8" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="D3" s="8" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="B1" s="6" t="s">
-        <x:v>22</x:v>
+      <x:c r="E3" s="8" t="s">
+        <x:v>39</x:v>
       </x:c>
-      <x:c r="C1" s="6" t="s">
-        <x:v>47</x:v>
+      <x:c r="F3" s="8" t="s">
+        <x:v>37</x:v>
       </x:c>
-      <x:c r="D1" s="6" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="E1" s="6" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="F1" s="6" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="G1" s="6" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="H1" s="6" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="I1" s="6" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="J1" s="6" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="K1" s="6" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="L1" s="21" t="s">
+      <x:c r="G3" s="8" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="M1" s="21" t="s">
-        <x:v>19</x:v>
+      <x:c r="H3" s="8" t="s">
+        <x:v>18</x:v>
       </x:c>
-    </x:row>
-    <x:row r="2" spans="1:14" s="7" customFormat="1" ht="13.199999999999999">
-      <x:c r="A2" s="6" t="s">
+      <x:c r="I3" s="8" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="J3" s="8" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="K3" s="8" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="L3" s="22" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="M3" s="22" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="N3" s="9"/>
+    </x:row>
+    <x:row r="4" spans="1:23" s="14" customFormat="1" ht="15.75" customHeight="1">
+      <x:c r="A4" s="11" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B4" s="11" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="B2" s="6" t="s">
-        <x:v>28</x:v>
+      <x:c r="C4" s="11" t="s">
+        <x:v>64</x:v>
       </x:c>
-      <x:c r="C2" s="6" t="s">
-        <x:v>28</x:v>
+      <x:c r="D4" s="11" t="s">
+        <x:v>52</x:v>
       </x:c>
-      <x:c r="D2" s="6" t="s">
-        <x:v>28</x:v>
+      <x:c r="E4" s="11" t="s">
+        <x:v>3</x:v>
       </x:c>
-      <x:c r="E2" s="6" t="s">
-        <x:v>28</x:v>
+      <x:c r="F4" s="11" t="s">
+        <x:v>53</x:v>
       </x:c>
-      <x:c r="F2" s="6" t="s">
-        <x:v>28</x:v>
+      <x:c r="G4" s="11" t="s">
+        <x:v>53</x:v>
       </x:c>
-      <x:c r="G2" s="6" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="H2" s="6" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="I2" s="6" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="J2" s="6" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="K2" s="6" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="L2" s="21" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="M2" s="21" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="N2" s="6"/>
-    </x:row>
-    <x:row r="3" spans="1:14" s="10" customFormat="1" ht="15.75" customHeight="1">
-      <x:c r="A3" s="8" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="B3" s="8" t="s">
+      <x:c r="H4" s="11" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="C3" s="8" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="D3" s="8" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="E3" s="8" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="F3" s="8" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="G3" s="8" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H3" s="8" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="I3" s="8" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J3" s="8" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="K3" s="8" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="L3" s="22" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="M3" s="22" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="N3" s="9"/>
-    </x:row>
-    <x:row r="4" spans="1:23" s="14" customFormat="1" ht="15.75" customHeight="1">
-      <x:c r="A4" s="11" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="B4" s="11" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C4" s="11" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="D4" s="11" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="E4" s="11" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="F4" s="11" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="G4" s="11" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="H4" s="11" t="s">
-        <x:v>65</x:v>
-      </x:c>
       <x:c r="I4" s="11" t="s">
-        <x:v>34</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J4" s="11">
         <x:v>1</x:v>
@@ -1529,7 +1529,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="M4" s="24" t="s">
-        <x:v>67</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N4" s="13"/>
       <x:c r="O4" s="12"/>
@@ -1544,31 +1544,31 @@
     </x:row>
     <x:row r="5" spans="1:23" s="7" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A5" s="15" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B5" s="15" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C5" s="15" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="D5" s="15" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="E5" s="16" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F5" s="31" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="B5" s="15" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C5" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D5" s="15" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="E5" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="F5" s="31" t="s">
-        <x:v>38</x:v>
-      </x:c>
       <x:c r="G5" s="15" t="s">
-        <x:v>38</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="H5" s="31" t="s">
-        <x:v>65</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="I5" s="15" t="s">
-        <x:v>34</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J5" s="15">
         <x:v>1</x:v>
@@ -1580,7 +1580,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="M5" s="25" t="s">
-        <x:v>68</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="N5" s="17"/>
       <x:c r="O5" s="17"/>
@@ -1595,31 +1595,31 @@
     </x:row>
     <x:row r="6" spans="1:23" s="7" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A6" s="15" t="s">
-        <x:v>55</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B6" s="15" t="s">
-        <x:v>9</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C6" s="15" t="s">
-        <x:v>48</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D6" s="15" t="s">
-        <x:v>39</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E6" s="16" t="s">
-        <x:v>14</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F6" s="31" t="s">
-        <x:v>38</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="G6" s="15" t="s">
-        <x:v>38</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="H6" s="31" t="s">
-        <x:v>65</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="I6" s="15" t="s">
-        <x:v>34</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J6" s="15">
         <x:v>1</x:v>
@@ -1631,7 +1631,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="M6" s="25" t="s">
-        <x:v>64</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="N6" s="17"/>
       <x:c r="O6" s="17"/>
@@ -1646,31 +1646,31 @@
     </x:row>
     <x:row r="7" spans="1:23" s="7" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A7" s="15" t="s">
-        <x:v>58</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B7" s="15" t="s">
-        <x:v>12</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C7" s="15" t="s">
-        <x:v>41</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D7" s="15" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E7" s="15" t="s">
-        <x:v>16</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F7" s="16" t="s">
-        <x:v>38</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="G7" s="15" t="s">
-        <x:v>38</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="H7" s="15" t="s">
-        <x:v>65</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="I7" s="15" t="s">
-        <x:v>34</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J7" s="15">
         <x:v>1</x:v>
@@ -1682,7 +1682,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="M7" s="25" t="s">
-        <x:v>56</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="N7" s="17"/>
       <x:c r="O7" s="17"/>
@@ -1697,31 +1697,31 @@
     </x:row>
     <x:row r="8" spans="1:23" s="7" customFormat="1" ht="13.199999999999999">
       <x:c r="A8" s="15" t="s">
-        <x:v>54</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B8" s="15" t="s">
-        <x:v>11</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C8" s="15" t="s">
-        <x:v>50</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D8" s="15" t="s">
-        <x:v>30</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E8" s="18" t="s">
-        <x:v>60</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F8" s="16" t="s">
-        <x:v>38</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="G8" s="15" t="s">
-        <x:v>38</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="H8" s="15" t="s">
-        <x:v>65</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="I8" s="15" t="s">
-        <x:v>34</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J8" s="15">
         <x:v>1</x:v>
@@ -1733,7 +1733,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="M8" s="26" t="s">
-        <x:v>63</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="N8" s="17"/>
       <x:c r="O8" s="17"/>
@@ -1748,31 +1748,31 @@
     </x:row>
     <x:row r="9" spans="1:23" s="7" customFormat="1" ht="13.199999999999999">
       <x:c r="A9" s="15" t="s">
-        <x:v>61</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B9" s="15" t="s">
-        <x:v>13</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C9" s="15" t="s">
-        <x:v>31</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D9" s="15" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="E9" s="18" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="E9" s="18" t="s">
-        <x:v>17</x:v>
-      </x:c>
       <x:c r="F9" s="16" t="s">
-        <x:v>38</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="G9" s="15" t="s">
-        <x:v>38</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="H9" s="15" t="s">
-        <x:v>65</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="I9" s="15" t="s">
-        <x:v>34</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J9" s="15">
         <x:v>1</x:v>
@@ -1784,7 +1784,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="M9" s="25" t="s">
-        <x:v>62</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="N9" s="17"/>
       <x:c r="O9" s="17"/>
@@ -1799,31 +1799,31 @@
     </x:row>
     <x:row r="10" spans="1:23" s="7" customFormat="1" ht="13.199999999999999">
       <x:c r="A10" s="15" t="s">
-        <x:v>57</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B10" s="15" t="s">
-        <x:v>6</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C10" s="15" t="s">
-        <x:v>37</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D10" s="15" t="s">
-        <x:v>33</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E10" s="6" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F10" s="18" t="s">
-        <x:v>38</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="G10" s="15" t="s">
-        <x:v>38</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="H10" s="15" t="s">
-        <x:v>65</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="I10" s="15" t="s">
-        <x:v>34</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J10" s="15">
         <x:v>1</x:v>
@@ -1835,7 +1835,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="M10" s="25" t="s">
-        <x:v>24</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="N10" s="17"/>
       <x:c r="O10" s="17"/>

--- a/JsonConverter/ExcelFiles/EnemySkill.xlsx
+++ b/JsonConverter/ExcelFiles/EnemySkill.xlsx
@@ -21,16 +21,49 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="73">
   <x:si>
-    <x:t>텍스처가 덜 입혀진 몸으로 그냥 부딪힘</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대충 만든 슬라임이라 펀치도 흐물흐물함</x:t>
-  </x:si>
-  <x:si>
     <x:t>눈에서 나가는 레이저인데 딱 봐도 이펙트가 싸구려임</x:t>
   </x:si>
   <x:si>
-    <x:t>Untextured Slam</x:t>
+    <x:t>Pulse Shot</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TargetType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cheap Bite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RandomEnemy</x:t>
+  </x:si>
+  <x:si>
+    <x:t>타겟 선택 방식</x:t>
+  </x:si>
+  <x:si>
+    <x:t>enemy_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Fake Laser</x:t>
+  </x:si>
+  <x:si>
+    <x:t>재사용 대기시간</x:t>
+  </x:si>
+  <x:si>
+    <x:t>enemy_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TargetCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ActionType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>적ID</x:t>
   </x:si>
   <x:si>
     <x:t>int</x:t>
@@ -39,22 +72,112 @@
     <x:t>위력</x:t>
   </x:si>
   <x:si>
+    <x:t>센티널</x:t>
+  </x:si>
+  <x:si>
     <x:t>설명</x:t>
   </x:si>
   <x:si>
-    <x:t>ID</x:t>
+    <x:t>스킬타입</x:t>
   </x:si>
   <x:si>
-    <x:t>적ID</x:t>
+    <x:t>Single</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EnemyId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>행동타입</x:t>
+  </x:si>
+  <x:si>
+    <x:t>괴성지르기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>레이저쏘기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>임시적03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>물어뜯기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>타겟 수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>펄스 사격</x:t>
+  </x:si>
+  <x:si>
+    <x:t>임시적05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>임시적07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스킬이름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>임시적04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>적 이름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스킬ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Power</x:t>
+  </x:si>
+  <x:si>
+    <x:t>임시적06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>타겟 범위</x:t>
+  </x:si>
+  <x:si>
+    <x:t>휘두르기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>삐걱펀치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>블랙가드 사격</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스킬이름영문</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Attack</x:t>
+  </x:si>
+  <x:si>
+    <x:t>블랙가드 병사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TargetSelectType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>enemySkill_07_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>enemySkill_05_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>저예산 좀비라 이빨 모델링이 대충임</x:t>
+  </x:si>
+  <x:si>
+    <x:t>enemySkill_06_01</x:t>
   </x:si>
   <x:si>
     <x:t>SkillDescription</x:t>
   </x:si>
   <x:si>
-    <x:t>enemySkill_07_01</x:t>
+    <x:t>enemySkill_03_01</x:t>
   </x:si>
   <x:si>
-    <x:t>enemySkill_03_01</x:t>
+    <x:t>Recycled Screech</x:t>
   </x:si>
   <x:si>
     <x:t>enemySkill_02_01</x:t>
@@ -66,178 +189,55 @@
     <x:t>enemySkill_01_01</x:t>
   </x:si>
   <x:si>
-    <x:t>저예산 좀비라 이빨 모델링이 대충임</x:t>
+    <x:t>SkillNameEn</x:t>
   </x:si>
   <x:si>
-    <x:t>enemySkill_06_01</x:t>
+    <x:t>enemy_02</x:t>
   </x:si>
   <x:si>
-    <x:t>enemySkill_05_01</x:t>
+    <x:t>EnemyName</x:t>
   </x:si>
   <x:si>
-    <x:t>TargetSelectType</x:t>
+    <x:t>enemy_06</x:t>
   </x:si>
   <x:si>
-    <x:t>Recycled Screech</x:t>
+    <x:t>enemy_05</x:t>
   </x:si>
   <x:si>
-    <x:t>SkillType</x:t>
+    <x:t>Wobbly Whip</x:t>
   </x:si>
   <x:si>
-    <x:t>Fake Laser</x:t>
+    <x:t>Rusty Punch</x:t>
   </x:si>
   <x:si>
-    <x:t>타겟 선택 방식</x:t>
+    <x:t>CoolTime</x:t>
   </x:si>
   <x:si>
-    <x:t>enemy_03</x:t>
+    <x:t>SkillName</x:t>
   </x:si>
   <x:si>
-    <x:t>TargetType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TargetCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>재사용 대기시간</x:t>
-  </x:si>
-  <x:si>
-    <x:t>enemy_07</x:t>
+    <x:t>enemy_04</x:t>
   </x:si>
   <x:si>
     <x:t>enemy_01</x:t>
   </x:si>
   <x:si>
-    <x:t>enemy_02</x:t>
+    <x:t>Blackguard Shot</x:t>
   </x:si>
   <x:si>
-    <x:t>enemy_06</x:t>
+    <x:t>팔에 장착된 펄스 건으로 에너지 탄환을 발사함</x:t>
   </x:si>
   <x:si>
-    <x:t>Rusty Punch</x:t>
+    <x:t>블랙가드의 제식 소총으로 적을 조준해 사격함</x:t>
   </x:si>
   <x:si>
-    <x:t>Maybe Punch</x:t>
-  </x:si>
-  <x:si>
-    <x:t>enemy_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cheap Bite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Wobbly Whip</x:t>
-  </x:si>
-  <x:si>
-    <x:t>enemy_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ActionType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CoolTime</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkillNameEn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkillName</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EnemyName</x:t>
+    <x:t>관절 렌더링이 덜 돼서 삐걱거리며 팔을 휘두름</x:t>
   </x:si>
   <x:si>
     <x:t>다른 게임에서 가져온 듯한 효과음으로 괴성을 지름</x:t>
   </x:si>
   <x:si>
-    <x:t>관절 렌더링이 덜 돼서 삐걱거리며 팔을 휘두름</x:t>
-  </x:si>
-  <x:si>
     <x:t>물리 연산이 이상해서 촉수가 제멋대로 흐느적거림</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스킬ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>레이저쏘기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>임시적04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>타겟 범위</x:t>
-  </x:si>
-  <x:si>
-    <x:t>행동타입</x:t>
-  </x:si>
-  <x:si>
-    <x:t>물어뜯기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Single</x:t>
-  </x:si>
-  <x:si>
-    <x:t>몸통박치기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Attack</x:t>
-  </x:si>
-  <x:si>
-    <x:t>타겟 수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>임시적07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>휘두르기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>삐걱펀치</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스킬이름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>임시적05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EnemyId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>임시적03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스킬이름영문</x:t>
-  </x:si>
-  <x:si>
-    <x:t>적 이름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>임시적01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대충펀치</x:t>
-  </x:si>
-  <x:si>
-    <x:t>임시적06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스킬타입</x:t>
-  </x:si>
-  <x:si>
-    <x:t>괴성지르기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>임시적02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Power</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RandomEnemy</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1368,156 +1368,156 @@
   <x:sheetData>
     <x:row r="1" spans="1:13" s="7" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A1" s="6" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B1" s="6" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C1" s="6" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="D1" s="6" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E1" s="6" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F1" s="6" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="G1" s="6" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="H1" s="6" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="I1" s="6" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="J1" s="6" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="K1" s="6" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="L1" s="21" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="M1" s="21" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:14" s="7" customFormat="1" ht="13.199999999999999">
+      <x:c r="A2" s="6" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B2" s="6" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C2" s="6" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D2" s="6" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E2" s="6" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="F2" s="6" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="G2" s="6" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H2" s="6" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="I2" s="6" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="J2" s="6" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="K2" s="6" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="L2" s="21" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="M2" s="21" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="N2" s="6"/>
+    </x:row>
+    <x:row r="3" spans="1:14" s="10" customFormat="1" ht="15.75" customHeight="1">
+      <x:c r="A3" s="8" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B3" s="8" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C3" s="8" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="D3" s="8" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="E3" s="8" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F3" s="8" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G3" s="8" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="H3" s="8" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="B1" s="6" t="s">
-        <x:v>8</x:v>
+      <x:c r="I3" s="8" t="s">
+        <x:v>2</x:v>
       </x:c>
-      <x:c r="C1" s="6" t="s">
+      <x:c r="J3" s="8" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K3" s="8" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="D1" s="6" t="s">
-        <x:v>58</x:v>
+      <x:c r="L3" s="22" t="s">
+        <x:v>36</x:v>
       </x:c>
-      <x:c r="E1" s="6" t="s">
-        <x:v>62</x:v>
+      <x:c r="M3" s="22" t="s">
+        <x:v>50</x:v>
       </x:c>
-      <x:c r="F1" s="6" t="s">
-        <x:v>49</x:v>
+      <x:c r="N3" s="9"/>
+    </x:row>
+    <x:row r="4" spans="1:23" s="14" customFormat="1" ht="15.75" customHeight="1">
+      <x:c r="A4" s="11" t="s">
+        <x:v>55</x:v>
       </x:c>
-      <x:c r="G1" s="6" t="s">
-        <x:v>68</x:v>
+      <x:c r="B4" s="11" t="s">
+        <x:v>66</x:v>
       </x:c>
-      <x:c r="H1" s="6" t="s">
-        <x:v>22</x:v>
+      <x:c r="C4" s="11" t="s">
+        <x:v>44</x:v>
       </x:c>
-      <x:c r="I1" s="6" t="s">
-        <x:v>48</x:v>
+      <x:c r="D4" s="11" t="s">
+        <x:v>41</x:v>
       </x:c>
-      <x:c r="J1" s="6" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="K1" s="6" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="L1" s="21" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="M1" s="21" t="s">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:14" s="7" customFormat="1" ht="13.199999999999999">
-      <x:c r="A2" s="6" t="s">
+      <x:c r="E4" s="11" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="B2" s="6" t="s">
-        <x:v>67</x:v>
+      <x:c r="F4" s="11" t="s">
+        <x:v>43</x:v>
       </x:c>
-      <x:c r="C2" s="6" t="s">
-        <x:v>67</x:v>
+      <x:c r="G4" s="11" t="s">
+        <x:v>43</x:v>
       </x:c>
-      <x:c r="D2" s="6" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="E2" s="6" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="F2" s="6" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="G2" s="6" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="H2" s="6" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="I2" s="6" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="J2" s="6" t="s">
+      <x:c r="H4" s="11" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="K2" s="6" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="L2" s="21" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="M2" s="21" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="N2" s="6"/>
-    </x:row>
-    <x:row r="3" spans="1:14" s="10" customFormat="1" ht="15.75" customHeight="1">
-      <x:c r="A3" s="8" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B3" s="8" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="C3" s="8" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="D3" s="8" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E3" s="8" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="F3" s="8" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="G3" s="8" t="s">
+      <x:c r="I4" s="11" t="s">
         <x:v>20</x:v>
-      </x:c>
-      <x:c r="H3" s="8" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="I3" s="8" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="J3" s="8" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="K3" s="8" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="L3" s="22" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="M3" s="22" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="N3" s="9"/>
-    </x:row>
-    <x:row r="4" spans="1:23" s="14" customFormat="1" ht="15.75" customHeight="1">
-      <x:c r="A4" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="B4" s="11" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C4" s="11" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="D4" s="11" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E4" s="11" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F4" s="11" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="G4" s="11" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="H4" s="11" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="I4" s="11" t="s">
-        <x:v>51</x:v>
       </x:c>
       <x:c r="J4" s="11">
         <x:v>1</x:v>
@@ -1526,10 +1526,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L4" s="23">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="M4" s="24" t="s">
-        <x:v>0</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="N4" s="13"/>
       <x:c r="O4" s="12"/>
@@ -1544,31 +1544,31 @@
     </x:row>
     <x:row r="5" spans="1:23" s="7" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A5" s="15" t="s">
-        <x:v>12</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B5" s="15" t="s">
-        <x:v>29</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C5" s="15" t="s">
-        <x:v>70</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D5" s="15" t="s">
-        <x:v>65</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E5" s="16" t="s">
-        <x:v>32</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F5" s="31" t="s">
-        <x:v>53</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="G5" s="15" t="s">
-        <x:v>53</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="H5" s="31" t="s">
-        <x:v>72</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="I5" s="15" t="s">
-        <x:v>51</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J5" s="15">
         <x:v>1</x:v>
@@ -1577,10 +1577,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L5" s="21">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="M5" s="25" t="s">
-        <x:v>1</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="N5" s="17"/>
       <x:c r="O5" s="17"/>
@@ -1595,31 +1595,31 @@
     </x:row>
     <x:row r="6" spans="1:23" s="7" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A6" s="15" t="s">
-        <x:v>11</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B6" s="15" t="s">
-        <x:v>23</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C6" s="15" t="s">
-        <x:v>61</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D6" s="15" t="s">
-        <x:v>57</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E6" s="16" t="s">
-        <x:v>31</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F6" s="31" t="s">
-        <x:v>53</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="G6" s="15" t="s">
-        <x:v>53</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="H6" s="31" t="s">
-        <x:v>72</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="I6" s="15" t="s">
-        <x:v>51</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J6" s="15">
         <x:v>1</x:v>
@@ -1631,7 +1631,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="M6" s="25" t="s">
-        <x:v>43</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="N6" s="17"/>
       <x:c r="O6" s="17"/>
@@ -1646,31 +1646,31 @@
     </x:row>
     <x:row r="7" spans="1:23" s="7" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A7" s="15" t="s">
-        <x:v>13</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B7" s="15" t="s">
-        <x:v>36</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C7" s="15" t="s">
-        <x:v>47</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D7" s="15" t="s">
-        <x:v>50</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E7" s="15" t="s">
-        <x:v>34</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F7" s="16" t="s">
-        <x:v>53</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="G7" s="15" t="s">
-        <x:v>53</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="H7" s="15" t="s">
-        <x:v>72</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="I7" s="15" t="s">
-        <x:v>51</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J7" s="15">
         <x:v>1</x:v>
@@ -1682,7 +1682,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="M7" s="25" t="s">
-        <x:v>15</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="N7" s="17"/>
       <x:c r="O7" s="17"/>
@@ -1697,31 +1697,31 @@
     </x:row>
     <x:row r="8" spans="1:23" s="7" customFormat="1" ht="13.199999999999999">
       <x:c r="A8" s="15" t="s">
-        <x:v>17</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B8" s="15" t="s">
-        <x:v>33</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C8" s="15" t="s">
-        <x:v>59</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D8" s="15" t="s">
-        <x:v>69</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E8" s="18" t="s">
-        <x:v>19</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F8" s="16" t="s">
-        <x:v>53</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="G8" s="15" t="s">
-        <x:v>53</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="H8" s="15" t="s">
-        <x:v>72</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="I8" s="15" t="s">
-        <x:v>51</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J8" s="15">
         <x:v>1</x:v>
@@ -1733,7 +1733,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="M8" s="26" t="s">
-        <x:v>42</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="N8" s="17"/>
       <x:c r="O8" s="17"/>
@@ -1748,31 +1748,31 @@
     </x:row>
     <x:row r="9" spans="1:23" s="7" customFormat="1" ht="13.199999999999999">
       <x:c r="A9" s="15" t="s">
-        <x:v>16</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B9" s="15" t="s">
-        <x:v>30</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C9" s="15" t="s">
-        <x:v>66</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D9" s="15" t="s">
-        <x:v>56</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E9" s="18" t="s">
-        <x:v>35</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F9" s="16" t="s">
-        <x:v>53</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="G9" s="15" t="s">
-        <x:v>53</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="H9" s="15" t="s">
-        <x:v>72</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="I9" s="15" t="s">
-        <x:v>51</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J9" s="15">
         <x:v>1</x:v>
@@ -1784,7 +1784,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="M9" s="25" t="s">
-        <x:v>44</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="N9" s="17"/>
       <x:c r="O9" s="17"/>
@@ -1799,31 +1799,31 @@
     </x:row>
     <x:row r="10" spans="1:23" s="7" customFormat="1" ht="13.199999999999999">
       <x:c r="A10" s="15" t="s">
-        <x:v>10</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B10" s="15" t="s">
-        <x:v>27</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C10" s="15" t="s">
-        <x:v>55</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D10" s="15" t="s">
-        <x:v>46</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E10" s="6" t="s">
-        <x:v>21</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F10" s="18" t="s">
-        <x:v>53</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="G10" s="15" t="s">
-        <x:v>53</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="H10" s="15" t="s">
-        <x:v>72</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="I10" s="15" t="s">
-        <x:v>51</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J10" s="15">
         <x:v>1</x:v>
@@ -1835,7 +1835,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="M10" s="25" t="s">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N10" s="17"/>
       <x:c r="O10" s="17"/>
